--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/NEVADA_2023.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/NEVADA_2023.xlsx
@@ -3804,7 +3804,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C192">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C324">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Huichapa</t>
+          <t>Huichapan</t>
         </is>
       </c>
       <c r="C444">
